--- a/极印版 aiken/销量概率模型/AiKen销量概率分布_读数表.xlsx
+++ b/极印版 aiken/销量概率模型/AiKen销量概率分布_读数表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nan\Documents\GitHub\code_aiken\极印版 aiken\销量概率模型\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911EC5D7-D095-4326-A749-4B6CF7D85714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F02A088-AAF2-4918-A358-07A66973F491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="读图说明" sheetId="1" r:id="rId1"/>
@@ -880,10 +880,12 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>

--- a/极印版 aiken/销量概率模型/AiKen销量概率分布_读数表.xlsx
+++ b/极印版 aiken/销量概率模型/AiKen销量概率分布_读数表.xlsx
@@ -8,38 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nan\Documents\GitHub\code_aiken\极印版 aiken\销量概率模型\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F02A088-AAF2-4918-A358-07A66973F491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766FE9E4-41A6-4B86-AD94-021BA44B6431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="读图说明" sheetId="1" r:id="rId1"/>
     <sheet name="分位表" sheetId="2" r:id="rId2"/>
     <sheet name="直方图数据" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="93">
   <si>
     <t>AiKen 销量概率分布 · 读数表</t>
   </si>
   <si>
+    <t>模型 v0.3 · 8,000 次蒙特卡洛 · 漏斗参数已按 S1 实测校准（CPM 37.6/45.2 · CTR 2.14% · CVR 0.98%；数据源：极印投放数据 2026-10-26）</t>
+  </si>
+  <si>
     <t>这个分布是什么？</t>
   </si>
   <si>
@@ -124,7 +114,7 @@
     <t>90.0%</t>
   </si>
   <si>
-    <t>Worst 场景锚（月销 ≈ 1,459）</t>
+    <t>Worst 场景锚（月销 ≈ 1,192）</t>
   </si>
   <si>
     <t>P15</t>
@@ -175,7 +165,7 @@
     <t>50.0%</t>
   </si>
   <si>
-    <t>Normal 场景锚（月销 ≈ 2,196）</t>
+    <t>Normal 场景锚（月销 ≈ 1,834）</t>
   </si>
   <si>
     <t>P55</t>
@@ -226,7 +216,7 @@
     <t>10.0%</t>
   </si>
   <si>
-    <t>Best 场景锚（月销 ≈ 3,137）</t>
+    <t>Best 场景锚（月销 ≈ 2,678）</t>
   </si>
   <si>
     <t>P95</t>
@@ -247,28 +237,34 @@
     <t>三年累计</t>
   </si>
   <si>
-    <t>98.2%</t>
-  </si>
-  <si>
-    <t>94.9%</t>
-  </si>
-  <si>
-    <t>87.1%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>75.2%</t>
+    <t>98.9%</t>
+  </si>
+  <si>
+    <t>96.4%</t>
+  </si>
+  <si>
+    <t>90.7%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>70.3%</t>
+  </si>
+  <si>
+    <t>P(≥ 100,000 台) — 十万台线</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>12.0%</t>
+  </si>
+  <si>
+    <t>P(≥ 200,000 台)</t>
+  </si>
+  <si>
+    <t>注：本表由 v0.3 模拟结果（v03_results.npz）直接计算生成；漏斗参数为 S1 实测校准（2026-10-26）。</t>
   </si>
   <si>
     <t>直方图原始数据（可选中后插入 Excel 图表）</t>
@@ -295,35 +291,19 @@
     <t>三年占比</t>
   </si>
   <si>
-    <t>模型 v0.3 · 8,000 次蒙特卡洛 · 漏斗参数已按 S1 实测校准（CPM 37.6/45.2 · CTR 2.14% · CVR 0.98%；数据源：极印投放数据 2026-10-26）</t>
+    <t>P(≥ Worst 锚 14,300 台) — P10</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>P(≥ Worst 锚 17,513 台) — P10</t>
+    <t>P(≥ Normal 锚 22,009 台) — P50</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>P(≥ Normal 锚 26,348 台) — P50</t>
+    <t>P(≥ Best 锚 32,139 台) — P90</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>P(≥ Best 锚 37,643 台) — P90</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>P(≥ 50,000 台)</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(≥ 100,000 台) — 十万台线</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(≥ 200,000 台)</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>注：本表由 v0.3 模拟结果（v03_results.npz）直接计算生成；漏斗参数为 S1 实测校准（2026-10-26）。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -808,63 +788,63 @@
     </row>
     <row r="3" spans="2:3" ht="15.6">
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="45" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1">
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="45" customHeight="1">
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="60" customHeight="1">
       <c r="B8" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="75" customHeight="1">
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="60" customHeight="1">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="60" customHeight="1">
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -880,590 +860,588 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="20.399999999999999">
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15.6">
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="16.2">
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="15.6">
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6">
-        <v>15177</v>
+        <v>12684</v>
       </c>
       <c r="D6" s="6">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="6">
-        <v>26195</v>
+        <v>25314</v>
       </c>
       <c r="G6" s="6">
-        <v>2.62</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="2:9" ht="16.2">
       <c r="B7" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7">
-        <v>17513</v>
+        <v>14300</v>
       </c>
       <c r="D7" s="7">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="7">
-        <v>33960</v>
+        <v>32985</v>
       </c>
       <c r="G7" s="7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="15.6">
       <c r="B8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="6">
-        <v>18955</v>
+        <v>15679</v>
       </c>
       <c r="D8" s="6">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="6">
-        <v>39920</v>
+        <v>38369</v>
       </c>
       <c r="G8" s="6">
-        <v>3.99</v>
+        <v>3.84</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="2:9" ht="15.6">
       <c r="B9" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="9">
-        <v>20174</v>
+        <v>16728</v>
       </c>
       <c r="D9" s="9">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" s="9">
-        <v>45695</v>
+        <v>42525</v>
       </c>
       <c r="G9" s="9">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I9" s="10"/>
     </row>
     <row r="10" spans="2:9" ht="15.6">
       <c r="B10" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="6">
-        <v>21295</v>
+        <v>17704</v>
       </c>
       <c r="D10" s="6">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" s="6">
-        <v>50237</v>
+        <v>46528</v>
       </c>
       <c r="G10" s="6">
-        <v>5.0199999999999996</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="2:9" ht="15.6">
       <c r="B11" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="9">
-        <v>22433</v>
+        <v>18582</v>
       </c>
       <c r="D11" s="9">
-        <v>2.2400000000000002</v>
+        <v>1.86</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" s="9">
-        <v>54747</v>
+        <v>50155</v>
       </c>
       <c r="G11" s="9">
-        <v>5.47</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" s="10"/>
     </row>
     <row r="12" spans="2:9" ht="15.6">
       <c r="B12" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="6">
-        <v>23404</v>
+        <v>19408</v>
       </c>
       <c r="D12" s="6">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" s="6">
-        <v>59297</v>
+        <v>53609</v>
       </c>
       <c r="G12" s="6">
-        <v>5.93</v>
+        <v>5.36</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="2:9" ht="15.6">
       <c r="B13" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="9">
-        <v>24347</v>
+        <v>20300</v>
       </c>
       <c r="D13" s="9">
-        <v>2.4300000000000002</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" s="9">
-        <v>63309</v>
+        <v>56728</v>
       </c>
       <c r="G13" s="9">
-        <v>6.33</v>
+        <v>5.67</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="2:9" ht="15.6">
       <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" s="6">
-        <v>25370</v>
+        <v>21139</v>
       </c>
       <c r="D14" s="6">
-        <v>2.54</v>
+        <v>2.11</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F14" s="6">
-        <v>67487</v>
+        <v>59881</v>
       </c>
       <c r="G14" s="6">
-        <v>6.75</v>
+        <v>5.99</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="2:9" ht="32.4">
       <c r="B15" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="7">
-        <v>26348</v>
+        <v>22009</v>
       </c>
       <c r="D15" s="7">
-        <v>2.63</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="7">
-        <v>71179</v>
+        <v>63130</v>
       </c>
       <c r="G15" s="7">
-        <v>7.12</v>
+        <v>6.31</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="15.6">
       <c r="B16" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="6">
-        <v>27400</v>
+        <v>22905</v>
       </c>
       <c r="D16" s="6">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="6">
-        <v>75381</v>
+        <v>66642</v>
       </c>
       <c r="G16" s="6">
-        <v>7.54</v>
+        <v>6.66</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="2:9" ht="15.6">
       <c r="B17" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="9">
-        <v>28444</v>
+        <v>23827</v>
       </c>
       <c r="D17" s="9">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="9">
-        <v>79280</v>
+        <v>70036</v>
       </c>
       <c r="G17" s="9">
-        <v>7.93</v>
+        <v>7</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I17" s="10"/>
     </row>
     <row r="18" spans="2:9" ht="15.6">
       <c r="B18" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="6">
-        <v>29531</v>
+        <v>24744</v>
       </c>
       <c r="D18" s="6">
-        <v>2.95</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="6">
-        <v>84128</v>
+        <v>74037</v>
       </c>
       <c r="G18" s="6">
-        <v>8.41</v>
+        <v>7.4</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="2:9" ht="15.6">
       <c r="B19" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="9">
-        <v>30724</v>
+        <v>25874</v>
       </c>
       <c r="D19" s="9">
-        <v>3.07</v>
+        <v>2.59</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="9">
-        <v>89356</v>
+        <v>78392</v>
       </c>
       <c r="G19" s="9">
-        <v>8.94</v>
+        <v>7.84</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I19" s="10"/>
     </row>
     <row r="20" spans="2:9" ht="15.6">
       <c r="B20" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="6">
-        <v>32002</v>
+        <v>26996</v>
       </c>
       <c r="D20" s="6">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="6">
-        <v>94393</v>
+        <v>82997</v>
       </c>
       <c r="G20" s="6">
-        <v>9.44</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="2:9" ht="15.6">
       <c r="B21" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="9">
-        <v>33510</v>
+        <v>28337</v>
       </c>
       <c r="D21" s="9">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" s="9">
-        <v>101082</v>
+        <v>88338</v>
       </c>
       <c r="G21" s="9">
-        <v>10.11</v>
+        <v>8.83</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="2:9" ht="15.6">
       <c r="B22" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="6">
-        <v>35268</v>
+        <v>29861</v>
       </c>
       <c r="D22" s="6">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="6">
-        <v>109495</v>
+        <v>95003</v>
       </c>
       <c r="G22" s="6">
-        <v>10.95</v>
+        <v>9.5</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="2:9" ht="16.2">
       <c r="B23" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="7">
-        <v>37643</v>
+        <v>32139</v>
       </c>
       <c r="D23" s="7">
-        <v>3.76</v>
+        <v>3.21</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="7">
-        <v>119858</v>
+        <v>103850</v>
       </c>
       <c r="G23" s="7">
-        <v>11.99</v>
+        <v>10.39</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="15.6">
       <c r="B24" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" s="6">
-        <v>41555</v>
+        <v>35600</v>
       </c>
       <c r="D24" s="6">
-        <v>4.16</v>
+        <v>3.56</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F24" s="6">
-        <v>134992</v>
+        <v>119747</v>
       </c>
       <c r="G24" s="6">
-        <v>13.5</v>
+        <v>11.97</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="26" spans="2:9" ht="17.399999999999999">
       <c r="B26" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="16.2">
       <c r="B27" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="78">
       <c r="B28" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="78">
       <c r="B29" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="2:9" ht="62.4">
       <c r="B30" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="46.8">
       <c r="B31" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="62.4">
       <c r="B32" s="4" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="46.8">
       <c r="B33" s="10" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>77</v>
@@ -1471,7 +1449,7 @@
     </row>
     <row r="35" spans="2:4" ht="15">
       <c r="B35" s="12" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1486,32 +1464,31 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="20.399999999999999">
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="15.6">
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="16.2">
       <c r="B5" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="15.6">
@@ -1533,7 +1510,7 @@
         <v>3636</v>
       </c>
       <c r="D7" s="13">
-        <v>3.7500000000000001E-4</v>
+        <v>2.5000000000000001E-4</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.6">
@@ -1544,7 +1521,7 @@
         <v>5454</v>
       </c>
       <c r="D8" s="13">
-        <v>1.1249999999999999E-3</v>
+        <v>6.2500000000000001E-4</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15.6">
@@ -1555,7 +1532,7 @@
         <v>7272</v>
       </c>
       <c r="D9" s="13">
-        <v>1.5E-3</v>
+        <v>2.3749999999999999E-3</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15.6">
@@ -1566,7 +1543,7 @@
         <v>9090</v>
       </c>
       <c r="D10" s="13">
-        <v>2.875E-3</v>
+        <v>5.2500000000000003E-3</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="15.6">
@@ -1577,7 +1554,7 @@
         <v>10909</v>
       </c>
       <c r="D11" s="13">
-        <v>4.875E-3</v>
+        <v>1.3625E-2</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="15.6">
@@ -1588,7 +1565,7 @@
         <v>12727</v>
       </c>
       <c r="D12" s="13">
-        <v>0.01</v>
+        <v>2.9125000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.6">
@@ -1599,7 +1576,7 @@
         <v>14545</v>
       </c>
       <c r="D13" s="13">
-        <v>2.1000000000000001E-2</v>
+        <v>5.6125000000000001E-2</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="15.6">
@@ -1610,7 +1587,7 @@
         <v>16363</v>
       </c>
       <c r="D14" s="13">
-        <v>0.03</v>
+        <v>7.3999999999999996E-2</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="15.6">
@@ -1621,7 +1598,7 @@
         <v>18181</v>
       </c>
       <c r="D15" s="13">
-        <v>5.0375000000000003E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="15.6">
@@ -1632,7 +1609,7 @@
         <v>20000</v>
       </c>
       <c r="D16" s="13">
-        <v>6.9625000000000006E-2</v>
+        <v>0.10875</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="15.6">
@@ -1643,7 +1620,7 @@
         <v>21818</v>
       </c>
       <c r="D17" s="13">
-        <v>8.1500000000000003E-2</v>
+        <v>0.10725</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="15.6">
@@ -1654,7 +1631,7 @@
         <v>23636</v>
       </c>
       <c r="D18" s="13">
-        <v>8.7249999999999994E-2</v>
+        <v>0.10037500000000001</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="15.6">
@@ -1665,7 +1642,7 @@
         <v>25454</v>
       </c>
       <c r="D19" s="13">
-        <v>9.4E-2</v>
+        <v>9.1374999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="15.6">
@@ -1676,7 +1653,7 @@
         <v>27272</v>
       </c>
       <c r="D20" s="13">
-        <v>8.9624999999999996E-2</v>
+        <v>7.825E-2</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="15.6">
@@ -1687,7 +1664,7 @@
         <v>29090</v>
       </c>
       <c r="D21" s="13">
-        <v>8.4000000000000005E-2</v>
+        <v>6.5125000000000002E-2</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="15.6">
@@ -1698,7 +1675,7 @@
         <v>30909</v>
       </c>
       <c r="D22" s="13">
-        <v>7.9750000000000001E-2</v>
+        <v>4.7875000000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="15.6">
@@ -1709,7 +1686,7 @@
         <v>32727</v>
       </c>
       <c r="D23" s="13">
-        <v>6.5375000000000003E-2</v>
+        <v>3.5125000000000003E-2</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="15.6">
@@ -1720,7 +1697,7 @@
         <v>34545</v>
       </c>
       <c r="D24" s="13">
-        <v>5.5875000000000001E-2</v>
+        <v>2.8125000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="15.6">
@@ -1731,7 +1708,7 @@
         <v>36363</v>
       </c>
       <c r="D25" s="13">
-        <v>4.6124999999999999E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="15.6">
@@ -1742,7 +1719,7 @@
         <v>38181</v>
       </c>
       <c r="D26" s="13">
-        <v>3.2250000000000001E-2</v>
+        <v>1.4874999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="15.6">
@@ -1753,7 +1730,7 @@
         <v>40000</v>
       </c>
       <c r="D27" s="13">
-        <v>2.4875000000000001E-2</v>
+        <v>9.3749999999999997E-3</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="15.6">
@@ -1764,7 +1741,7 @@
         <v>41818</v>
       </c>
       <c r="D28" s="13">
-        <v>1.9375E-2</v>
+        <v>5.875E-3</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="15.6">
@@ -1775,7 +1752,7 @@
         <v>43636</v>
       </c>
       <c r="D29" s="13">
-        <v>1.4375000000000001E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="15.6">
@@ -1786,7 +1763,7 @@
         <v>45454</v>
       </c>
       <c r="D30" s="13">
-        <v>1.1124999999999999E-2</v>
+        <v>3.1250000000000002E-3</v>
       </c>
     </row>
     <row r="31" spans="2:4" ht="15.6">
@@ -1797,7 +1774,7 @@
         <v>47272</v>
       </c>
       <c r="D31" s="13">
-        <v>7.2500000000000004E-3</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="15.6">
@@ -1808,7 +1785,7 @@
         <v>49090</v>
       </c>
       <c r="D32" s="13">
-        <v>5.7499999999999999E-3</v>
+        <v>1.6249999999999999E-3</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="15.6">
@@ -1819,7 +1796,7 @@
         <v>50909</v>
       </c>
       <c r="D33" s="13">
-        <v>4.2500000000000003E-3</v>
+        <v>7.5000000000000002E-4</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="15.6">
@@ -1830,7 +1807,7 @@
         <v>52727</v>
       </c>
       <c r="D34" s="13">
-        <v>1.75E-3</v>
+        <v>3.7500000000000001E-4</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="15.6">
@@ -1841,7 +1818,7 @@
         <v>54545</v>
       </c>
       <c r="D35" s="13">
-        <v>1E-3</v>
+        <v>2.5000000000000001E-4</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="15.6">
@@ -1852,7 +1829,7 @@
         <v>56363</v>
       </c>
       <c r="D36" s="13">
-        <v>1E-3</v>
+        <v>1.25E-4</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="15.6">
@@ -1863,7 +1840,7 @@
         <v>58181</v>
       </c>
       <c r="D37" s="13">
-        <v>8.7500000000000002E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="15.6">
@@ -1874,7 +1851,7 @@
         <v>60000</v>
       </c>
       <c r="D38" s="13">
-        <v>3.7500000000000001E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="15.6">
@@ -1885,7 +1862,7 @@
         <v>61818</v>
       </c>
       <c r="D39" s="13">
-        <v>3.7500000000000001E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="15.6">
@@ -1907,7 +1884,7 @@
         <v>65454</v>
       </c>
       <c r="D41" s="13">
-        <v>1.25E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="15.6">
@@ -2000,13 +1977,13 @@
     </row>
     <row r="52" spans="2:4" ht="16.2">
       <c r="B52" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="2:4" ht="15.6">
@@ -2017,7 +1994,7 @@
         <v>5000</v>
       </c>
       <c r="D53" s="13">
-        <v>3.7500000000000001E-4</v>
+        <v>2.5000000000000001E-4</v>
       </c>
     </row>
     <row r="54" spans="2:4" ht="15.6">
@@ -2028,7 +2005,7 @@
         <v>10000</v>
       </c>
       <c r="D54" s="13">
-        <v>3.375E-3</v>
+        <v>3.2499999999999999E-3</v>
       </c>
     </row>
     <row r="55" spans="2:4" ht="15.6">
@@ -2039,7 +2016,7 @@
         <v>15000</v>
       </c>
       <c r="D55" s="13">
-        <v>7.4999999999999997E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
     </row>
     <row r="56" spans="2:4" ht="15.6">
@@ -2050,7 +2027,7 @@
         <v>20000</v>
       </c>
       <c r="D56" s="13">
-        <v>1.35E-2</v>
+        <v>1.5375E-2</v>
       </c>
     </row>
     <row r="57" spans="2:4" ht="15.6">
@@ -2061,7 +2038,7 @@
         <v>25000</v>
       </c>
       <c r="D57" s="13">
-        <v>2.0500000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="58" spans="2:4" ht="15.6">
@@ -2072,7 +2049,7 @@
         <v>30000</v>
       </c>
       <c r="D58" s="13">
-        <v>2.9125000000000002E-2</v>
+        <v>3.2250000000000001E-2</v>
       </c>
     </row>
     <row r="59" spans="2:4" ht="15.6">
@@ -2083,7 +2060,7 @@
         <v>35000</v>
       </c>
       <c r="D59" s="13">
-        <v>3.4125000000000003E-2</v>
+        <v>3.5374999999999997E-2</v>
       </c>
     </row>
     <row r="60" spans="2:4" ht="15.6">
@@ -2094,7 +2071,7 @@
         <v>40000</v>
       </c>
       <c r="D60" s="13">
-        <v>4.2250000000000003E-2</v>
+        <v>5.3874999999999999E-2</v>
       </c>
     </row>
     <row r="61" spans="2:4" ht="15.6">
@@ -2105,7 +2082,7 @@
         <v>45000</v>
       </c>
       <c r="D61" s="13">
-        <v>4.2625000000000003E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="62" spans="2:4" ht="15.6">
@@ -2116,7 +2093,7 @@
         <v>50000</v>
       </c>
       <c r="D62" s="13">
-        <v>5.4875E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
     </row>
     <row r="63" spans="2:4" ht="15.6">
@@ -2127,7 +2104,7 @@
         <v>55000</v>
       </c>
       <c r="D63" s="13">
-        <v>5.5E-2</v>
+        <v>7.5249999999999997E-2</v>
       </c>
     </row>
     <row r="64" spans="2:4" ht="15.6">
@@ -2138,7 +2115,7 @@
         <v>60000</v>
       </c>
       <c r="D64" s="13">
-        <v>5.5625000000000001E-2</v>
+        <v>7.85E-2</v>
       </c>
     </row>
     <row r="65" spans="2:4" ht="15.6">
@@ -2149,7 +2126,7 @@
         <v>65000</v>
       </c>
       <c r="D65" s="13">
-        <v>6.0374999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="15.6">
@@ -2160,7 +2137,7 @@
         <v>70000</v>
       </c>
       <c r="D66" s="13">
-        <v>6.3125000000000001E-2</v>
+        <v>7.3249999999999996E-2</v>
       </c>
     </row>
     <row r="67" spans="2:4" ht="15.6">
@@ -2171,7 +2148,7 @@
         <v>75000</v>
       </c>
       <c r="D67" s="13">
-        <v>6.4500000000000002E-2</v>
+        <v>6.1874999999999999E-2</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="15.6">
@@ -2182,7 +2159,7 @@
         <v>80000</v>
       </c>
       <c r="D68" s="13">
-        <v>5.9749999999999998E-2</v>
+        <v>5.9624999999999997E-2</v>
       </c>
     </row>
     <row r="69" spans="2:4" ht="15.6">
@@ -2193,7 +2170,7 @@
         <v>85000</v>
       </c>
       <c r="D69" s="13">
-        <v>5.2249999999999998E-2</v>
+        <v>4.9750000000000003E-2</v>
       </c>
     </row>
     <row r="70" spans="2:4" ht="15.6">
@@ -2204,7 +2181,7 @@
         <v>90000</v>
       </c>
       <c r="D70" s="13">
-        <v>4.8625000000000002E-2</v>
+        <v>4.4749999999999998E-2</v>
       </c>
     </row>
     <row r="71" spans="2:4" ht="15.6">
@@ -2215,7 +2192,7 @@
         <v>95000</v>
       </c>
       <c r="D71" s="13">
-        <v>4.6375E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="15.6">
@@ -2226,7 +2203,7 @@
         <v>100000</v>
       </c>
       <c r="D72" s="13">
-        <v>3.6999999999999998E-2</v>
+        <v>2.9749999999999999E-2</v>
       </c>
     </row>
     <row r="73" spans="2:4" ht="15.6">
@@ -2237,7 +2214,7 @@
         <v>105000</v>
       </c>
       <c r="D73" s="13">
-        <v>3.4625000000000003E-2</v>
+        <v>2.5250000000000002E-2</v>
       </c>
     </row>
     <row r="74" spans="2:4" ht="15.6">
@@ -2248,7 +2225,7 @@
         <v>110000</v>
       </c>
       <c r="D74" s="13">
-        <v>2.725E-2</v>
+        <v>1.925E-2</v>
       </c>
     </row>
     <row r="75" spans="2:4" ht="15.6">
@@ -2259,7 +2236,7 @@
         <v>115000</v>
       </c>
       <c r="D75" s="13">
-        <v>2.5250000000000002E-2</v>
+        <v>1.4250000000000001E-2</v>
       </c>
     </row>
     <row r="76" spans="2:4" ht="15.6">
@@ -2270,7 +2247,7 @@
         <v>120000</v>
       </c>
       <c r="D76" s="13">
-        <v>2.2624999999999999E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="77" spans="2:4" ht="15.6">
@@ -2281,7 +2258,7 @@
         <v>125000</v>
       </c>
       <c r="D77" s="13">
-        <v>1.8124999999999999E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="78" spans="2:4" ht="15.6">
@@ -2292,7 +2269,7 @@
         <v>130000</v>
       </c>
       <c r="D78" s="13">
-        <v>1.7375000000000002E-2</v>
+        <v>9.1249999999999994E-3</v>
       </c>
     </row>
     <row r="79" spans="2:4" ht="15.6">
@@ -2303,7 +2280,7 @@
         <v>135000</v>
       </c>
       <c r="D79" s="13">
-        <v>1.3875E-2</v>
+        <v>7.1250000000000003E-3</v>
       </c>
     </row>
     <row r="80" spans="2:4" ht="15.6">
@@ -2314,7 +2291,7 @@
         <v>140000</v>
       </c>
       <c r="D80" s="13">
-        <v>1.0874999999999999E-2</v>
+        <v>5.2500000000000003E-3</v>
       </c>
     </row>
     <row r="81" spans="2:4" ht="15.6">
@@ -2325,7 +2302,7 @@
         <v>145000</v>
       </c>
       <c r="D81" s="13">
-        <v>5.7499999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="82" spans="2:4" ht="15.6">
@@ -2336,7 +2313,7 @@
         <v>150000</v>
       </c>
       <c r="D82" s="13">
-        <v>6.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="83" spans="2:4" ht="15.6">
@@ -2347,7 +2324,7 @@
         <v>155000</v>
       </c>
       <c r="D83" s="13">
-        <v>6.4999999999999997E-3</v>
+        <v>2.3749999999999999E-3</v>
       </c>
     </row>
     <row r="84" spans="2:4" ht="15.6">
@@ -2358,7 +2335,7 @@
         <v>160000</v>
       </c>
       <c r="D84" s="13">
-        <v>6.1250000000000002E-3</v>
+        <v>1.8749999999999999E-3</v>
       </c>
     </row>
     <row r="85" spans="2:4" ht="15.6">
@@ -2369,7 +2346,7 @@
         <v>165000</v>
       </c>
       <c r="D85" s="13">
-        <v>2.7499999999999998E-3</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="86" spans="2:4" ht="15.6">
@@ -2380,7 +2357,7 @@
         <v>170000</v>
       </c>
       <c r="D86" s="13">
-        <v>2.875E-3</v>
+        <v>6.2500000000000001E-4</v>
       </c>
     </row>
     <row r="87" spans="2:4" ht="15.6">
@@ -2391,7 +2368,7 @@
         <v>175000</v>
       </c>
       <c r="D87" s="13">
-        <v>1.5E-3</v>
+        <v>8.7500000000000002E-4</v>
       </c>
     </row>
     <row r="88" spans="2:4" ht="15.6">
@@ -2402,7 +2379,7 @@
         <v>180000</v>
       </c>
       <c r="D88" s="13">
-        <v>2E-3</v>
+        <v>3.7500000000000001E-4</v>
       </c>
     </row>
     <row r="89" spans="2:4" ht="15.6">
@@ -2413,7 +2390,7 @@
         <v>185000</v>
       </c>
       <c r="D89" s="13">
-        <v>1.5E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="90" spans="2:4" ht="15.6">
@@ -2424,7 +2401,7 @@
         <v>190000</v>
       </c>
       <c r="D90" s="13">
-        <v>1.1249999999999999E-3</v>
+        <v>7.5000000000000002E-4</v>
       </c>
     </row>
     <row r="91" spans="2:4" ht="15.6">
@@ -2435,7 +2412,7 @@
         <v>195000</v>
       </c>
       <c r="D91" s="13">
-        <v>2.5000000000000001E-4</v>
+        <v>3.7500000000000001E-4</v>
       </c>
     </row>
     <row r="92" spans="2:4" ht="15.6">
@@ -2446,7 +2423,7 @@
         <v>200000</v>
       </c>
       <c r="D92" s="13">
-        <v>1.1249999999999999E-3</v>
+        <v>1.25E-4</v>
       </c>
     </row>
   </sheetData>
